--- a/artfynd/A 42203-2025 artfynd.xlsx
+++ b/artfynd/A 42203-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>132433115</v>
       </c>
       <c r="B5" t="n">
-        <v>97208</v>
+        <v>97211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>132433114</v>
       </c>
       <c r="B6" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>132433116</v>
       </c>
       <c r="B9" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>132433121</v>
       </c>
       <c r="B10" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,48 +1578,60 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132433120</v>
+        <v>132433113</v>
       </c>
       <c r="B11" t="n">
-        <v>79315</v>
+        <v>57136</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Burtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591406</v>
+        <v>591421</v>
       </c>
       <c r="R11" t="n">
-        <v>6965970</v>
+        <v>6965896</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1675,60 +1687,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132433113</v>
+        <v>132433120</v>
       </c>
       <c r="B12" t="n">
-        <v>57136</v>
+        <v>79317</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Burtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591421</v>
+        <v>591406</v>
       </c>
       <c r="R12" t="n">
-        <v>6965896</v>
+        <v>6965970</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1784,32 +1784,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132433112</v>
+        <v>132433122</v>
       </c>
       <c r="B13" t="n">
-        <v>80448</v>
+        <v>92191</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591421</v>
+        <v>591499</v>
       </c>
       <c r="R13" t="n">
-        <v>6965885</v>
+        <v>6965894</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1881,32 +1881,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132433122</v>
+        <v>132433112</v>
       </c>
       <c r="B14" t="n">
-        <v>92188</v>
+        <v>80450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591499</v>
+        <v>591421</v>
       </c>
       <c r="R14" t="n">
-        <v>6965894</v>
+        <v>6965885</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>132433109</v>
       </c>
       <c r="B18" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 42203-2025 artfynd.xlsx
+++ b/artfynd/A 42203-2025 artfynd.xlsx
@@ -1578,60 +1578,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132433113</v>
+        <v>132433120</v>
       </c>
       <c r="B11" t="n">
-        <v>57136</v>
+        <v>79317</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Burtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591421</v>
+        <v>591406</v>
       </c>
       <c r="R11" t="n">
-        <v>6965896</v>
+        <v>6965970</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1687,48 +1675,60 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132433120</v>
+        <v>132433113</v>
       </c>
       <c r="B12" t="n">
-        <v>79317</v>
+        <v>57136</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Burtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591406</v>
+        <v>591421</v>
       </c>
       <c r="R12" t="n">
-        <v>6965970</v>
+        <v>6965896</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 42203-2025 artfynd.xlsx
+++ b/artfynd/A 42203-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>132433115</v>
       </c>
       <c r="B5" t="n">
-        <v>97211</v>
+        <v>97219</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>132433114</v>
       </c>
       <c r="B6" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>132433123</v>
       </c>
       <c r="B7" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132433124</v>
+        <v>132433116</v>
       </c>
       <c r="B8" t="n">
-        <v>57945</v>
+        <v>79319</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591524</v>
+        <v>591349</v>
       </c>
       <c r="R8" t="n">
-        <v>6965883</v>
+        <v>6965971</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Med  apothecier</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132433116</v>
+        <v>132433124</v>
       </c>
       <c r="B9" t="n">
-        <v>79317</v>
+        <v>57946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,13 +1414,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591349</v>
+        <v>591524</v>
       </c>
       <c r="R9" t="n">
-        <v>6965971</v>
+        <v>6965883</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Med  apothecier</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1484,7 +1484,7 @@
         <v>132433121</v>
       </c>
       <c r="B10" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>132433120</v>
       </c>
       <c r="B11" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>132433113</v>
       </c>
       <c r="B12" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>132433122</v>
       </c>
       <c r="B13" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>132433112</v>
       </c>
       <c r="B14" t="n">
-        <v>80450</v>
+        <v>80452</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>132433118</v>
       </c>
       <c r="B15" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>132433110</v>
       </c>
       <c r="B16" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>132433111</v>
       </c>
       <c r="B17" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>132433109</v>
       </c>
       <c r="B18" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 42203-2025 artfynd.xlsx
+++ b/artfynd/A 42203-2025 artfynd.xlsx
@@ -1277,7 +1277,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132433116</v>
+        <v>132433121</v>
       </c>
       <c r="B8" t="n">
         <v>79319</v>
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591349</v>
+        <v>591432</v>
       </c>
       <c r="R8" t="n">
-        <v>6965971</v>
+        <v>6965949</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1348,11 +1348,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Med  apothecier</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132433124</v>
+        <v>132433116</v>
       </c>
       <c r="B9" t="n">
-        <v>57946</v>
+        <v>79319</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,13 +1409,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591524</v>
+        <v>591349</v>
       </c>
       <c r="R9" t="n">
-        <v>6965883</v>
+        <v>6965971</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1454,7 +1449,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Med  apothecier</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1481,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132433121</v>
+        <v>132433124</v>
       </c>
       <c r="B10" t="n">
-        <v>79319</v>
+        <v>57946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591432</v>
+        <v>591524</v>
       </c>
       <c r="R10" t="n">
-        <v>6965949</v>
+        <v>6965883</v>
       </c>
       <c r="S10" t="n">
         <v>11</v>
@@ -1552,6 +1547,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,48 +1578,60 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132433120</v>
+        <v>132433113</v>
       </c>
       <c r="B11" t="n">
-        <v>79319</v>
+        <v>57137</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Burtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591406</v>
+        <v>591421</v>
       </c>
       <c r="R11" t="n">
-        <v>6965970</v>
+        <v>6965896</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1675,60 +1687,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132433113</v>
+        <v>132433120</v>
       </c>
       <c r="B12" t="n">
-        <v>57137</v>
+        <v>79319</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Burtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591421</v>
+        <v>591406</v>
       </c>
       <c r="R12" t="n">
-        <v>6965896</v>
+        <v>6965970</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1784,32 +1784,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132433122</v>
+        <v>132433112</v>
       </c>
       <c r="B13" t="n">
-        <v>92197</v>
+        <v>80452</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591499</v>
+        <v>591421</v>
       </c>
       <c r="R13" t="n">
-        <v>6965894</v>
+        <v>6965885</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1881,32 +1881,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132433112</v>
+        <v>132433122</v>
       </c>
       <c r="B14" t="n">
-        <v>80452</v>
+        <v>92197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591421</v>
+        <v>591499</v>
       </c>
       <c r="R14" t="n">
-        <v>6965885</v>
+        <v>6965894</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 42203-2025 artfynd.xlsx
+++ b/artfynd/A 42203-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>132433115</v>
       </c>
       <c r="B5" t="n">
-        <v>97219</v>
+        <v>97229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>132433114</v>
       </c>
       <c r="B6" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>132433123</v>
       </c>
       <c r="B7" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132433121</v>
+        <v>132433124</v>
       </c>
       <c r="B8" t="n">
-        <v>79319</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591432</v>
+        <v>591524</v>
       </c>
       <c r="R8" t="n">
-        <v>6965949</v>
+        <v>6965883</v>
       </c>
       <c r="S8" t="n">
         <v>11</v>
@@ -1348,6 +1348,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,7 +1382,7 @@
         <v>132433116</v>
       </c>
       <c r="B9" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132433124</v>
+        <v>132433121</v>
       </c>
       <c r="B10" t="n">
-        <v>57946</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1492,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591524</v>
+        <v>591432</v>
       </c>
       <c r="R10" t="n">
-        <v>6965883</v>
+        <v>6965949</v>
       </c>
       <c r="S10" t="n">
         <v>11</v>
@@ -1547,11 +1552,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,60 +1578,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132433113</v>
+        <v>132433120</v>
       </c>
       <c r="B11" t="n">
-        <v>57137</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Burtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591421</v>
+        <v>591406</v>
       </c>
       <c r="R11" t="n">
-        <v>6965896</v>
+        <v>6965970</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1687,48 +1675,60 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132433120</v>
+        <v>132433113</v>
       </c>
       <c r="B12" t="n">
-        <v>79319</v>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Burtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591406</v>
+        <v>591421</v>
       </c>
       <c r="R12" t="n">
-        <v>6965970</v>
+        <v>6965896</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1784,32 +1784,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132433112</v>
+        <v>132433122</v>
       </c>
       <c r="B13" t="n">
-        <v>80452</v>
+        <v>92207</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591421</v>
+        <v>591499</v>
       </c>
       <c r="R13" t="n">
-        <v>6965885</v>
+        <v>6965894</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1881,32 +1881,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132433122</v>
+        <v>132433112</v>
       </c>
       <c r="B14" t="n">
-        <v>92197</v>
+        <v>80460</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591499</v>
+        <v>591421</v>
       </c>
       <c r="R14" t="n">
-        <v>6965894</v>
+        <v>6965885</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>132433118</v>
       </c>
       <c r="B15" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>132433110</v>
       </c>
       <c r="B16" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>132433111</v>
       </c>
       <c r="B17" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>132433109</v>
       </c>
       <c r="B18" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 42203-2025 artfynd.xlsx
+++ b/artfynd/A 42203-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>132433115</v>
       </c>
       <c r="B5" t="n">
-        <v>97229</v>
+        <v>97230</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>132433114</v>
       </c>
       <c r="B6" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132433124</v>
+        <v>132433116</v>
       </c>
       <c r="B8" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591524</v>
+        <v>591349</v>
       </c>
       <c r="R8" t="n">
-        <v>6965883</v>
+        <v>6965971</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Med  apothecier</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,7 +1379,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132433116</v>
+        <v>132433121</v>
       </c>
       <c r="B9" t="n">
         <v>79327</v>
@@ -1414,13 +1414,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591349</v>
+        <v>591432</v>
       </c>
       <c r="R9" t="n">
-        <v>6965971</v>
+        <v>6965949</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1450,11 +1450,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Med  apothecier</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1481,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132433121</v>
+        <v>132433124</v>
       </c>
       <c r="B10" t="n">
-        <v>79327</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591432</v>
+        <v>591524</v>
       </c>
       <c r="R10" t="n">
-        <v>6965949</v>
+        <v>6965883</v>
       </c>
       <c r="S10" t="n">
         <v>11</v>
@@ -1552,6 +1547,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,48 +1578,60 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132433120</v>
+        <v>132433113</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Burtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591406</v>
+        <v>591421</v>
       </c>
       <c r="R11" t="n">
-        <v>6965970</v>
+        <v>6965896</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1675,60 +1687,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132433113</v>
+        <v>132433120</v>
       </c>
       <c r="B12" t="n">
-        <v>57141</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Burtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591421</v>
+        <v>591406</v>
       </c>
       <c r="R12" t="n">
-        <v>6965896</v>
+        <v>6965970</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>132433122</v>
       </c>
       <c r="B13" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42203-2025 artfynd.xlsx
+++ b/artfynd/A 42203-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>132433115</v>
       </c>
       <c r="B5" t="n">
-        <v>97230</v>
+        <v>97231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1578,60 +1578,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132433113</v>
+        <v>132433120</v>
       </c>
       <c r="B11" t="n">
-        <v>57141</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Burtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591421</v>
+        <v>591406</v>
       </c>
       <c r="R11" t="n">
-        <v>6965896</v>
+        <v>6965970</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1687,48 +1675,60 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132433120</v>
+        <v>132433113</v>
       </c>
       <c r="B12" t="n">
-        <v>79327</v>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Burtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591406</v>
+        <v>591421</v>
       </c>
       <c r="R12" t="n">
-        <v>6965970</v>
+        <v>6965896</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1784,32 +1784,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132433122</v>
+        <v>132433112</v>
       </c>
       <c r="B13" t="n">
-        <v>92208</v>
+        <v>80460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591499</v>
+        <v>591421</v>
       </c>
       <c r="R13" t="n">
-        <v>6965894</v>
+        <v>6965885</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1881,32 +1881,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132433112</v>
+        <v>132433122</v>
       </c>
       <c r="B14" t="n">
-        <v>80460</v>
+        <v>92208</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591421</v>
+        <v>591499</v>
       </c>
       <c r="R14" t="n">
-        <v>6965885</v>
+        <v>6965894</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 42203-2025 artfynd.xlsx
+++ b/artfynd/A 42203-2025 artfynd.xlsx
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132433116</v>
+        <v>132433124</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591349</v>
+        <v>591524</v>
       </c>
       <c r="R8" t="n">
-        <v>6965971</v>
+        <v>6965883</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Med  apothecier</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,7 +1379,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132433121</v>
+        <v>132433116</v>
       </c>
       <c r="B9" t="n">
         <v>79327</v>
@@ -1414,13 +1414,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591432</v>
+        <v>591349</v>
       </c>
       <c r="R9" t="n">
-        <v>6965949</v>
+        <v>6965971</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1450,6 +1450,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Med  apothecier</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132433124</v>
+        <v>132433121</v>
       </c>
       <c r="B10" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1492,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591524</v>
+        <v>591432</v>
       </c>
       <c r="R10" t="n">
-        <v>6965883</v>
+        <v>6965949</v>
       </c>
       <c r="S10" t="n">
         <v>11</v>
@@ -1547,11 +1552,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1784,32 +1784,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132433112</v>
+        <v>132433122</v>
       </c>
       <c r="B13" t="n">
-        <v>80460</v>
+        <v>92208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591421</v>
+        <v>591499</v>
       </c>
       <c r="R13" t="n">
-        <v>6965885</v>
+        <v>6965894</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1881,32 +1881,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132433122</v>
+        <v>132433112</v>
       </c>
       <c r="B14" t="n">
-        <v>92208</v>
+        <v>80460</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591499</v>
+        <v>591421</v>
       </c>
       <c r="R14" t="n">
-        <v>6965894</v>
+        <v>6965885</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 42203-2025 artfynd.xlsx
+++ b/artfynd/A 42203-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>132433115</v>
       </c>
       <c r="B5" t="n">
-        <v>97231</v>
+        <v>97232</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>132433114</v>
       </c>
       <c r="B6" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>132433123</v>
       </c>
       <c r="B7" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132433124</v>
+        <v>132433116</v>
       </c>
       <c r="B8" t="n">
-        <v>57950</v>
+        <v>79328</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,13 +1312,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591524</v>
+        <v>591349</v>
       </c>
       <c r="R8" t="n">
-        <v>6965883</v>
+        <v>6965971</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Med  apothecier</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132433116</v>
+        <v>132433121</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1414,13 +1414,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591349</v>
+        <v>591432</v>
       </c>
       <c r="R9" t="n">
-        <v>6965971</v>
+        <v>6965949</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1450,11 +1450,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Med  apothecier</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1481,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132433121</v>
+        <v>132433124</v>
       </c>
       <c r="B10" t="n">
-        <v>79327</v>
+        <v>57951</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591432</v>
+        <v>591524</v>
       </c>
       <c r="R10" t="n">
-        <v>6965949</v>
+        <v>6965883</v>
       </c>
       <c r="S10" t="n">
         <v>11</v>
@@ -1552,6 +1547,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1581,7 +1581,7 @@
         <v>132433120</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>132433113</v>
       </c>
       <c r="B12" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>132433122</v>
       </c>
       <c r="B13" t="n">
-        <v>92208</v>
+        <v>92209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>132433112</v>
       </c>
       <c r="B14" t="n">
-        <v>80460</v>
+        <v>80461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>132433118</v>
       </c>
       <c r="B15" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>132433110</v>
       </c>
       <c r="B16" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>132433111</v>
       </c>
       <c r="B17" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>132433109</v>
       </c>
       <c r="B18" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
